--- a/sample_rooms.xlsx
+++ b/sample_rooms.xlsx
@@ -5,20 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8610590cbf95aee3/Desktop/Darsh/thesis-scheduler/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loaym\Documents\GitHub\thesis-scheduler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_F25DC773A252ABDACC104824611C5F9A5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E737ACF3-F23C-428E-9C14-D282964A1E7F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92A024E-AA1C-41E5-B8A6-96D8D0341EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="13758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -130,10 +141,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -399,75 +406,1399 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:A235"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.41796875" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f>A21+A20</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" ref="A23:A86" si="0">A22+A21</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>4647</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>7519</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>12166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>19685</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>31851</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>51536</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>83387</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>134923</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>218310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>353233</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>571543</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>924776</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>1496319</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>2421095</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>3917414</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>6338509</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>10255923</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>16594432</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>26850355</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>43444787</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>70295142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>113739929</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>184035071</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>297775000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>481810071</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>779585071</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>1261395142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>2040980213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>3302375355</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>5343355568</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>8645730923</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>13989086491</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>22634817414</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>36623903905</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>59258721319</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>95882625224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <f t="shared" si="0"/>
+        <v>155141346543</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <f t="shared" si="0"/>
+        <v>251023971767</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <f t="shared" si="0"/>
+        <v>406165318310</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <f t="shared" si="0"/>
+        <v>657189290077</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <f t="shared" si="0"/>
+        <v>1063354608387</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <f t="shared" si="0"/>
+        <v>1720543898464</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <f t="shared" si="0"/>
+        <v>2783898506851</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <f t="shared" si="0"/>
+        <v>4504442405315</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <f t="shared" si="0"/>
+        <v>7288340912166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <f t="shared" si="0"/>
+        <v>11792783317481</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <f t="shared" si="0"/>
+        <v>19081124229647</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <f t="shared" si="0"/>
+        <v>30873907547128</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <f t="shared" si="0"/>
+        <v>49955031776775</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <f t="shared" si="0"/>
+        <v>80828939323903</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <f t="shared" si="0"/>
+        <v>130783971100678</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <f t="shared" si="0"/>
+        <v>211612910424581</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <f t="shared" si="0"/>
+        <v>342396881525259</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <f t="shared" ref="A87:A150" si="1">A86+A85</f>
+        <v>554009791949840</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>896406673475099</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>1450416465424939</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>2346823138900038</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>3797239604324977</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>6144062743225015</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>9941302347549992</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>1.6085365090775008E+16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>2.6026667438325E+16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>4.2112032529100008E+16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>6.8138699967425008E+16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>1.1025073249652502E+17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>1.7838943246395002E+17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>2.8864016496047501E+17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>4.6702959742442502E+17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>7.556697623849001E+17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>1.2226993598093251E+18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>1.9783691221942252E+18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>3.2010684820035502E+18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>5.1794376041977754E+18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>8.3805060862013256E+18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>1.3559943690399101E+19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>2.1940449776600424E+19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>3.5500393466999525E+19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>5.7440843243599954E+19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>9.2941236710599475E+19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>1.5038207995419945E+20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>2.4332331666479894E+20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>3.9370539661899838E+20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>6.3702871328379739E+20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>1.0307341099027957E+21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>1.6677628231865931E+21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>2.6984969330893888E+21</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>4.3662597562759821E+21</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>7.0647566893653709E+21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>1.1431016445641354E+22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>1.8495773135006725E+22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>2.9926789580648077E+22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>4.8422562715654804E+22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>7.8349352296302881E+22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>1.2677191501195769E+23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>2.0512126730826055E+23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>3.3189318232021824E+23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>5.3701444962847879E+23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <f t="shared" si="1"/>
+        <v>8.6890763194869702E+23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <f t="shared" si="1"/>
+        <v>1.4059220815771759E+24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <f t="shared" si="1"/>
+        <v>2.274829713525873E+24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <f t="shared" si="1"/>
+        <v>3.6807517951030492E+24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <f t="shared" si="1"/>
+        <v>5.9555815086289227E+24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <f t="shared" si="1"/>
+        <v>9.6363333037319719E+24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <f t="shared" si="1"/>
+        <v>1.5591914812360895E+25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <f t="shared" si="1"/>
+        <v>2.5228248116092867E+25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <f t="shared" si="1"/>
+        <v>4.0820162928453757E+25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <f t="shared" si="1"/>
+        <v>6.6048411044546623E+25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <f t="shared" si="1"/>
+        <v>1.0686857397300037E+26</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <f t="shared" si="1"/>
+        <v>1.72916985017547E+26</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <f t="shared" si="1"/>
+        <v>2.7978555899054738E+26</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <f t="shared" si="1"/>
+        <v>4.5270254400809441E+26</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <f t="shared" si="1"/>
+        <v>7.3248810299864175E+26</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <f t="shared" si="1"/>
+        <v>1.1851906470067362E+27</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <f t="shared" si="1"/>
+        <v>1.9176787500053779E+27</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <f t="shared" si="1"/>
+        <v>3.1028693970121142E+27</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <f t="shared" si="1"/>
+        <v>5.0205481470174927E+27</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <f t="shared" si="1"/>
+        <v>8.1234175440296064E+27</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <f t="shared" ref="A151:A214" si="2">A150+A149</f>
+        <v>1.3143965691047099E+28</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <f t="shared" si="2"/>
+        <v>2.1267383235076708E+28</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <f t="shared" si="2"/>
+        <v>3.4411348926123805E+28</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <f t="shared" si="2"/>
+        <v>5.5678732161200512E+28</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <f t="shared" si="2"/>
+        <v>9.0090081087324308E+28</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <f t="shared" si="2"/>
+        <v>1.4576881324852482E+29</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <f t="shared" si="2"/>
+        <v>2.3585889433584915E+29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <f t="shared" si="2"/>
+        <v>3.8162770758437395E+29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <f t="shared" si="2"/>
+        <v>6.1748660192022309E+29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <f t="shared" si="2"/>
+        <v>9.9911430950459697E+29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <f t="shared" si="2"/>
+        <v>1.61660091142482E+30</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <f t="shared" si="2"/>
+        <v>2.615715220929417E+30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <f t="shared" si="2"/>
+        <v>4.2323161323542367E+30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <f t="shared" si="2"/>
+        <v>6.8480313532836542E+30</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <f t="shared" si="2"/>
+        <v>1.1080347485637891E+31</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <f t="shared" si="2"/>
+        <v>1.7928378838921545E+31</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <f t="shared" si="2"/>
+        <v>2.9008726324559438E+31</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>4.6937105163480983E+31</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>7.5945831488040422E+31</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>1.228829366515214E+32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <f t="shared" si="2"/>
+        <v>1.9882876813956182E+32</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <f t="shared" si="2"/>
+        <v>3.2171170479108322E+32</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <f t="shared" si="2"/>
+        <v>5.2054047293064504E+32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <f t="shared" si="2"/>
+        <v>8.422521777217283E+32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <f t="shared" si="2"/>
+        <v>1.3627926506523733E+33</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <f t="shared" si="2"/>
+        <v>2.2050448283741016E+33</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <f t="shared" si="2"/>
+        <v>3.5678374790264748E+33</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <f t="shared" si="2"/>
+        <v>5.7728823074005761E+33</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>9.3407197864270504E+33</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>1.5113602093827625E+34</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>2.4454321880254676E+34</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>3.9567923974082301E+34</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>6.4022245854336977E+34</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>1.0359016982841928E+35</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <f t="shared" si="2"/>
+        <v>1.6761241568275625E+35</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <f t="shared" si="2"/>
+        <v>2.7120258551117555E+35</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <f t="shared" si="2"/>
+        <v>4.388150011939318E+35</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <f t="shared" si="2"/>
+        <v>7.1001758670510728E+35</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <f t="shared" si="2"/>
+        <v>1.1488325878990391E+36</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <f t="shared" si="2"/>
+        <v>1.8588501746041465E+36</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <f t="shared" si="2"/>
+        <v>3.0076827625031854E+36</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <f t="shared" si="2"/>
+        <v>4.8665329371073319E+36</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <f t="shared" si="2"/>
+        <v>7.8742156996105174E+36</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <f t="shared" si="2"/>
+        <v>1.2740748636717848E+37</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <f t="shared" si="2"/>
+        <v>2.0614964336328367E+37</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <f t="shared" si="2"/>
+        <v>3.3355712973046215E+37</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <f t="shared" si="2"/>
+        <v>5.3970677309374581E+37</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <f t="shared" si="2"/>
+        <v>8.7326390282420792E+37</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <f t="shared" si="2"/>
+        <v>1.4129706759179536E+38</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <f t="shared" si="2"/>
+        <v>2.2862345787421616E+38</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <f t="shared" si="2"/>
+        <v>3.6992052546601148E+38</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <f t="shared" si="2"/>
+        <v>5.9854398334022764E+38</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <f t="shared" si="2"/>
+        <v>9.6846450880623919E+38</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <f t="shared" si="2"/>
+        <v>1.5670084921464669E+39</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <f t="shared" si="2"/>
+        <v>2.5354730009527061E+39</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <f t="shared" si="2"/>
+        <v>4.102481493099173E+39</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <f t="shared" si="2"/>
+        <v>6.6379544940518788E+39</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <f t="shared" si="2"/>
+        <v>1.0740435987151052E+40</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <f t="shared" si="2"/>
+        <v>1.7378390481202931E+40</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <f t="shared" si="2"/>
+        <v>2.8118826468353984E+40</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <f t="shared" si="2"/>
+        <v>4.5497216949556912E+40</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <f t="shared" si="2"/>
+        <v>7.3616043417910896E+40</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <f t="shared" si="2"/>
+        <v>1.1911326036746782E+41</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <f t="shared" si="2"/>
+        <v>1.9272930378537872E+41</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <f t="shared" ref="A215:A235" si="3">A214+A213</f>
+        <v>3.1184256415284654E+41</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <f t="shared" si="3"/>
+        <v>5.0457186793822523E+41</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <f t="shared" si="3"/>
+        <v>8.1641443209107169E+41</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <f t="shared" si="3"/>
+        <v>1.3209863000292969E+42</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <f t="shared" si="3"/>
+        <v>2.1374007321203686E+42</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <f t="shared" si="3"/>
+        <v>3.4583870321496652E+42</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <f t="shared" si="3"/>
+        <v>5.5957877642700338E+42</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <f t="shared" si="3"/>
+        <v>9.054174796419699E+42</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <f t="shared" si="3"/>
+        <v>1.4649962560689733E+43</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <f t="shared" si="3"/>
+        <v>2.3704137357109429E+43</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <f t="shared" si="3"/>
+        <v>3.835409991779916E+43</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <f t="shared" si="3"/>
+        <v>6.2058237274908589E+43</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <f t="shared" si="3"/>
+        <v>1.0041233719270775E+44</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <f t="shared" si="3"/>
+        <v>1.6247057446761633E+44</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <f t="shared" si="3"/>
+        <v>2.6288291166032408E+44</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <f t="shared" si="3"/>
+        <v>4.2535348612794037E+44</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <f t="shared" si="3"/>
+        <v>6.882363977882644E+44</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <f t="shared" si="3"/>
+        <v>1.1135898839162048E+45</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <f t="shared" si="3"/>
+        <v>1.8018262817044693E+45</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <f t="shared" si="3"/>
+        <v>2.9154161656206738E+45</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <f t="shared" si="3"/>
+        <v>4.7172424473251431E+45</v>
       </c>
     </row>
   </sheetData>
